--- a/artfynd/A 22036-2026 artfynd.xlsx
+++ b/artfynd/A 22036-2026 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134408722</v>
+        <v>134408660</v>
       </c>
       <c r="B2" t="n">
-        <v>58134</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,11 +703,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>stationär</t>
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468273</v>
+        <v>468300</v>
       </c>
       <c r="R2" t="n">
-        <v>6253580</v>
+        <v>6253561</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,7 +794,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -907,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134408660</v>
+        <v>134408722</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>58134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,16 +914,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,7 +931,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>stationär</t>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468300</v>
+        <v>468273</v>
       </c>
       <c r="R4" t="n">
-        <v>6253561</v>
+        <v>6253580</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +977,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
